--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-09-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-09-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A181AEE-E631-4803-A4C0-44F78EE0CB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531A0F83-8E57-484D-BDDC-67984AC23CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34935" yWindow="960" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="366">
   <si>
     <t>SKU</t>
   </si>
@@ -772,15 +772,9 @@
     <t>£1727.84</t>
   </si>
   <si>
-    <t>£14.65</t>
-  </si>
-  <si>
     <t>£16.7</t>
   </si>
   <si>
-    <t>£22.75</t>
-  </si>
-  <si>
     <t>£26.3</t>
   </si>
   <si>
@@ -799,9 +793,6 @@
     <t>£53.0</t>
   </si>
   <si>
-    <t>£1440.0</t>
-  </si>
-  <si>
     <t>£52.7</t>
   </si>
   <si>
@@ -1124,6 +1115,9 @@
   </si>
   <si>
     <t>£1,652.00</t>
+  </si>
+  <si>
+    <t>£1378.56</t>
   </si>
 </sst>
 </file>
@@ -1597,13 +1591,13 @@
         <v>243</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="Q2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="R2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1623,7 +1617,7 @@
         <v>120</v>
       </c>
       <c r="F3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G3" t="s">
         <v>101</v>
@@ -1653,13 +1647,13 @@
         <v>244</v>
       </c>
       <c r="P3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="R3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1679,7 +1673,7 @@
         <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G4" t="s">
         <v>102</v>
@@ -1691,7 +1685,7 @@
         <v>145</v>
       </c>
       <c r="J4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="K4" t="s">
         <v>184</v>
@@ -1712,10 +1706,10 @@
         <v>121</v>
       </c>
       <c r="Q4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="R4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1735,7 +1729,7 @@
         <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G5" t="s">
         <v>103</v>
@@ -1765,13 +1759,13 @@
         <v>76</v>
       </c>
       <c r="P5" t="s">
-        <v>252</v>
+        <v>122</v>
       </c>
       <c r="Q5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="R5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1791,7 +1785,7 @@
         <v>123</v>
       </c>
       <c r="F6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G6" t="s">
         <v>104</v>
@@ -1821,13 +1815,13 @@
         <v>245</v>
       </c>
       <c r="P6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="R6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1847,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G7" t="s">
         <v>105</v>
@@ -1880,10 +1874,10 @@
         <v>78</v>
       </c>
       <c r="Q7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="R7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1903,7 +1897,7 @@
         <v>124</v>
       </c>
       <c r="F8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G8" t="s">
         <v>106</v>
@@ -1915,7 +1909,7 @@
         <v>149</v>
       </c>
       <c r="J8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="K8" t="s">
         <v>188</v>
@@ -1936,10 +1930,10 @@
         <v>124</v>
       </c>
       <c r="Q8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="R8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1959,7 +1953,7 @@
         <v>125</v>
       </c>
       <c r="F9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G9" t="s">
         <v>107</v>
@@ -1971,7 +1965,7 @@
         <v>150</v>
       </c>
       <c r="J9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K9" t="s">
         <v>189</v>
@@ -1989,13 +1983,13 @@
         <v>79</v>
       </c>
       <c r="P9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -2015,7 +2009,7 @@
         <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G10" t="s">
         <v>108</v>
@@ -2045,13 +2039,13 @@
         <v>246</v>
       </c>
       <c r="P10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="R10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -2071,7 +2065,7 @@
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G11" t="s">
         <v>81</v>
@@ -2101,13 +2095,13 @@
         <v>247</v>
       </c>
       <c r="P11" t="s">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="Q11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="R11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -2127,7 +2121,7 @@
         <v>82</v>
       </c>
       <c r="F12" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G12" t="s">
         <v>109</v>
@@ -2157,13 +2151,13 @@
         <v>82</v>
       </c>
       <c r="P12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q12" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2183,7 +2177,7 @@
         <v>127</v>
       </c>
       <c r="F13" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G13" t="s">
         <v>110</v>
@@ -2195,7 +2189,7 @@
         <v>154</v>
       </c>
       <c r="J13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K13" t="s">
         <v>193</v>
@@ -2213,13 +2207,13 @@
         <v>83</v>
       </c>
       <c r="P13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="R13" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -2239,7 +2233,7 @@
         <v>128</v>
       </c>
       <c r="F14" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G14" t="s">
         <v>111</v>
@@ -2272,10 +2266,10 @@
         <v>128</v>
       </c>
       <c r="Q14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="R14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -2307,7 +2301,7 @@
         <v>156</v>
       </c>
       <c r="J15" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K15" t="s">
         <v>195</v>
@@ -2316,7 +2310,7 @@
         <v>99</v>
       </c>
       <c r="M15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="N15" t="s">
         <v>234</v>
@@ -2328,7 +2322,7 @@
         <v>129</v>
       </c>
       <c r="Q15" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="R15" t="s">
         <v>98</v>
@@ -2372,7 +2366,7 @@
         <v>99</v>
       </c>
       <c r="M16" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="N16" t="s">
         <v>235</v>
@@ -2381,13 +2375,13 @@
         <v>86</v>
       </c>
       <c r="P16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="R16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2407,7 +2401,7 @@
         <v>87</v>
       </c>
       <c r="F17" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G17" t="s">
         <v>98</v>
@@ -2428,7 +2422,7 @@
         <v>98</v>
       </c>
       <c r="M17" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="N17" t="s">
         <v>236</v>
@@ -2440,7 +2434,7 @@
         <v>87</v>
       </c>
       <c r="Q17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="R17" t="s">
         <v>98</v>
@@ -2484,22 +2478,22 @@
         <v>98</v>
       </c>
       <c r="M18" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N18" t="s">
         <v>237</v>
       </c>
       <c r="O18" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P18" t="s">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="Q18" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R18" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2519,7 +2513,7 @@
         <v>133</v>
       </c>
       <c r="F19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G19" t="s">
         <v>115</v>
@@ -2531,7 +2525,7 @@
         <v>160</v>
       </c>
       <c r="J19" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K19" t="s">
         <v>199</v>
@@ -2540,7 +2534,7 @@
         <v>99</v>
       </c>
       <c r="M19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="N19" t="s">
         <v>238</v>
@@ -2552,10 +2546,10 @@
         <v>133</v>
       </c>
       <c r="Q19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="R19" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2575,7 +2569,7 @@
         <v>116</v>
       </c>
       <c r="F20" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G20" t="s">
         <v>116</v>
@@ -2596,7 +2590,7 @@
         <v>99</v>
       </c>
       <c r="M20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="N20" t="s">
         <v>238</v>
@@ -2608,10 +2602,10 @@
         <v>116</v>
       </c>
       <c r="Q20" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="R20" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2631,7 +2625,7 @@
         <v>135</v>
       </c>
       <c r="F21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G21" t="s">
         <v>117</v>
@@ -2643,7 +2637,7 @@
         <v>161</v>
       </c>
       <c r="J21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="K21" t="s">
         <v>201</v>
@@ -2652,7 +2646,7 @@
         <v>99</v>
       </c>
       <c r="M21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="N21" t="s">
         <v>238</v>
@@ -2661,13 +2655,13 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q21" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="R21" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2678,16 +2672,16 @@
         <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E22" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -2699,7 +2693,7 @@
         <v>162</v>
       </c>
       <c r="J22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="K22" t="s">
         <v>202</v>
@@ -2708,22 +2702,22 @@
         <v>99</v>
       </c>
       <c r="M22" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="N22" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O22" t="s">
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="R22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2743,7 +2737,7 @@
         <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G23" t="s">
         <v>98</v>
@@ -2755,7 +2749,7 @@
         <v>163</v>
       </c>
       <c r="J23" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="K23" t="s">
         <v>203</v>
@@ -2764,7 +2758,7 @@
         <v>99</v>
       </c>
       <c r="M23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="N23" t="s">
         <v>239</v>
@@ -2776,10 +2770,10 @@
         <v>92</v>
       </c>
       <c r="Q23" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="R23" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2799,7 +2793,7 @@
         <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G24" t="s">
         <v>98</v>
@@ -2811,7 +2805,7 @@
         <v>164</v>
       </c>
       <c r="J24" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="K24" t="s">
         <v>203</v>
@@ -2820,7 +2814,7 @@
         <v>99</v>
       </c>
       <c r="M24" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="N24" t="s">
         <v>240</v>
@@ -2832,10 +2826,10 @@
         <v>93</v>
       </c>
       <c r="Q24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="R24" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2867,7 +2861,7 @@
         <v>98</v>
       </c>
       <c r="J25" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="K25" t="s">
         <v>98</v>
@@ -2876,7 +2870,7 @@
         <v>98</v>
       </c>
       <c r="M25" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="N25" t="s">
         <v>241</v>
@@ -2911,7 +2905,7 @@
         <v>95</v>
       </c>
       <c r="F26" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G26" t="s">
         <v>98</v>
@@ -2932,7 +2926,7 @@
         <v>99</v>
       </c>
       <c r="M26" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N26" t="s">
         <v>242</v>
@@ -2944,10 +2938,10 @@
         <v>95</v>
       </c>
       <c r="Q26" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="R26" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2958,16 +2952,16 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D27" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E27" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F27" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G27" t="s">
         <v>98</v>
@@ -2988,10 +2982,10 @@
         <v>99</v>
       </c>
       <c r="M27" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="N27" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O27" t="s">
         <v>249</v>
@@ -3000,10 +2994,10 @@
         <v>140</v>
       </c>
       <c r="Q27" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="R27" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3023,7 +3017,7 @@
         <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G28" t="s">
         <v>98</v>
@@ -3044,22 +3038,22 @@
         <v>99</v>
       </c>
       <c r="M28" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="N28" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="O28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="P28" t="s">
         <v>141</v>
       </c>
       <c r="Q28" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="R28" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3079,7 +3073,7 @@
         <v>97</v>
       </c>
       <c r="F29" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G29" t="s">
         <v>98</v>
@@ -3100,13 +3094,13 @@
         <v>98</v>
       </c>
       <c r="M29" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="N29" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O29" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="P29" t="s">
         <v>142</v>
@@ -3115,7 +3109,7 @@
         <v>98</v>
       </c>
       <c r="R29" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
